--- a/demo-StatsPAI-skill/tables/tableA1_robustness.xlsx
+++ b/demo-StatsPAI-skill/tables/tableA1_robustness.xlsx
@@ -53,7 +53,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -62,7 +62,30 @@
       <diagonal/>
     </border>
     <border>
-      <bottom style="medium"/>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -70,17 +93,23 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -449,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -472,183 +501,259 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>(1) Baseline OLS</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>(2) +Family bg</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>(3) Drop top 1% wage</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>(4) Drop bottom 1% wage</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>(5) Black only</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>(6) Non-black</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>(7) IQ-controlled</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>(8) 2SLS (nearc4)</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>(9) 2SLS (nearc2+nearc4)</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>(10) DML-PLR</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>(1) Baseline OLS</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>(2) +Family bg</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>(3) Drop top 1% wage</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>(4) Drop bottom 1% wage</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>(5) Black only</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>(6) Non-black</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>(7) IQ-controlled</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>(8) 2SLS (nearc4)</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>(9) 2SLS (nearc2+nearc4)</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>(10) DML-PLR</t>
-        </is>
-      </c>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>4.621***</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>4.524***</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>4.741***</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>4.695***</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>2.476***</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>4.686***</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>4.379***</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>3.666***</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>3.237***</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>(0.074)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>(0.088)</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>(0.072)</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>(0.072)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>(0.075)</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>(0.079)</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>(0.112)</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>(0.911)</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>(0.884)</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Years of schooling</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>0.075***</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>0.074***</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>0.069***</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>0.072***</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>0.071***</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>0.074***</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>0.070***</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>0.132**</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>0.157***</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>(0.004)</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>(0.005)</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>(0.004)</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>(0.004)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>(0.008)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>(0.004)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>(0.005)</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>(0.054)</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>(0.053)</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>First-stage F</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>13.26</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>7.89</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr"/>
@@ -656,96 +761,1560 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>exper</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>0.085***</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0.090***</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>0.079***</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>0.081***</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>0.034**</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>0.090***</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>0.095***</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>0.108***</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>0.119***</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>(0.007)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>(0.008)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>(0.007)</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>(0.006)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>(0.014)</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>(0.008)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>(0.009)</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>(0.023)</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>(0.023)</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>expersq</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>-0.003***</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>-0.002***</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>(0.001)</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>(0.000)</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>-0.199***</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>-0.165***</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>-0.193***</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>-0.189***</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2.476***</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>-0.148***</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>-0.147***</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>-0.123**</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>(0.018)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>(0.025)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>(0.018)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>(0.017)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>(0.075)</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>(0.028)</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>(0.053)</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>(0.052)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>south</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>-0.148***</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>-0.124***</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>-0.151***</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>-0.143***</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>-0.214***</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>-0.100***</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>-0.100***</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>-0.145***</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>-0.143***</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>(0.028)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>(0.034)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>(0.027)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>(0.026)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>(0.034)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>(0.017)</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>(0.035)</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>(0.029)</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>(0.030)</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>smsa</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>0.136***</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0.138***</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>0.131***</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>0.130***</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>0.143***</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>0.155***</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>0.123***</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>0.112***</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>0.101***</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>(0.019)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>(0.022)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>(0.019)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>(0.019)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>(0.033)</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>(0.017)</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>(0.023)</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>(0.031)</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>(0.031)</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>smsa66</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>0.026</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0.022</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>0.036</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>0.019</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>(0.019)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>(0.022)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>(0.018)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>(0.018)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>(0.022)</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>(0.021)</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>(0.021)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>reg662</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>0.096***</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0.089**</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>0.083**</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0.095***</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>0.103**</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>0.101***</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>0.103***</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>(0.035)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>(0.042)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>(0.035)</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>(0.034)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>(0.041)</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>(0.037)</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>(0.038)</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>reg663</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>0.145***</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0.121***</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>0.139***</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0.139***</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr"/>
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>0.126***</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>0.148***</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>0.150***</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>(0.034)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>(0.041)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>(0.034)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>(0.033)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>(0.040)</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>(0.036)</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>(0.037)</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>reg664</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0.039</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>0.053</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0.049</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>0.049</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>0.050</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>0.048</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>(0.041)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>(0.048)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>(0.041)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>(0.040)</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>(0.047)</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>(0.044)</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>(0.046)</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>reg665</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>0.128***</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0.095*</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>0.118***</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0.119***</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>0.124**</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>0.146***</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>0.154***</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>(0.043)</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>(0.052)</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>(0.042)</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>(0.041)</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>(0.053)</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>(0.049)</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>(0.051)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>reg666</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>0.141***</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0.108*</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>0.136***</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0.137***</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>0.159***</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>0.163***</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>0.173***</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>(0.045)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>(0.056)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>(0.045)</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>(0.043)</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>(0.058)</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>(0.052)</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>(0.054)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>reg667</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>0.118***</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0.101*</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>0.111**</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>0.121***</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>0.091</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>0.135***</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>0.142***</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>(0.046)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>(0.054)</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>(0.045)</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>(0.044)</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>(0.057)</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>(0.051)</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>(0.052)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>reg668</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>-0.056</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-0.068</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>-0.051</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>-0.048</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>-0.083</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>-0.095</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>(0.051)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>(0.060)</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>(0.051)</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>(0.048)</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>(0.059)</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>(0.057)</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>(0.059)</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>reg669</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>0.119***</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0.092**</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>0.101***</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>0.119***</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>0.122***</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>0.108***</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>0.103**</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>(0.039)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>(0.045)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>(0.038)</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>(0.038)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>(0.046)</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>(0.041)</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>(0.043)</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>fatheduc</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>-0.001</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>(0.003)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>motheduc</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0.008**</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr"/>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="5" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr"/>
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>(0.004)</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr"/>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>IQ</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>0.002***</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="5" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>(0.001)</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>ATE</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr"/>
+      <c r="C41" s="5" t="inlineStr"/>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr"/>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>0.074***</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr"/>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>(0.004)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>First-stage F</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr"/>
+      <c r="C43" s="5" t="inlineStr"/>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>13.26</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>7.89</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t>Hansen J p-value</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr"/>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>0.264</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>3,010</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>2,220</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>2,977</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>2,977</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>703</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>2,307</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>2,061</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>3,010</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>3,010</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>3,010</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>Standard errors in parentheses</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>* p&lt;0.10, ** p&lt;0.05, *** p&lt;0.01</t>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>*** p&lt;0.01, ** p&lt;0.05, * p&lt;0.10</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>